--- a/STP/presentations/Survey/survey_ST.xlsx
+++ b/STP/presentations/Survey/survey_ST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riccardo/Library/CloudStorage/Dropbox/RIKI/FAO/trainings/STP/presentations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Samue\Documents\trainings\STP\presentations\Survey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6B0E0A-716B-C948-A882-43EDDEA93AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A33EE5E-9172-4F67-BE8A-40A233471471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="2680" windowWidth="28040" windowHeight="17440" xr2:uid="{9F372B3D-94CE-0641-986A-C67A94B167DA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F372B3D-94CE-0641-986A-C67A94B167DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>type</t>
   </si>
   <si>
-    <t>participant_1</t>
-  </si>
-  <si>
     <t>participant_2</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>participant_33</t>
+  </si>
+  <si>
+    <t>question_number</t>
   </si>
 </sst>
 </file>
@@ -537,9 +537,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9071694-338F-9C4E-BE66-780AC1D3A6E8}">
   <dimension ref="A1:AI19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -547,106 +547,106 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>25</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>26</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>27</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>28</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>33</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>34</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>35</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>36</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>37</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>38</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>39</v>
       </c>
-      <c r="AI1" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -753,7 +753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -967,7 +967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>3</v>
       </c>
